--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_254_French_Guiana.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_254_French_Guiana.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R816f387fa3dd4fb7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8e1b85b83c044a70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R48ab202838154939"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R357a85e680eb4174"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re39eede6b1214191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re0c59734bb984268"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R5b6a0ab960f2471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R78640f9a157d43d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra6e343cba8554a65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rab1585a15862467e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rb755e8a785fd49a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb59a5c7ca66546fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ254CommercialTable" displayName="EEZ254CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ254CommercialTable" displayName="EEZ254CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ254FunctionalTable" displayName="EEZ254FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ254FunctionalTable" displayName="EEZ254FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ254ValidationTable" displayName="EEZ254ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ254ValidationTable" displayName="EEZ254ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5049,7 +5003,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd53cb4eed0ad4d34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30b50edb8f514db1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5059,20 +5013,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5080,444 +5024,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>280.7880275901</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.754489502744523</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>56.81846579025754</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>280.7880275901</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>56.86204486704058</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$66,A2,'Species'!$U$2:$U$66))</x:f>
-        <x:v>15966.181422956095</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.754489502744523</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>56.81846579025754</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>15953.944939941988</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>12.236483014106852</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000766987918046</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0007669879180460144</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>104.9707919169</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.6224362626007283</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>419.2144679251353</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>104.9707919169</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>423.4827478424323</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$66,A3,'Species'!$U$2:$U$66))</x:f>
-        <x:v>44453.31940416499</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.6224362626007283</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>419.2144679251353</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>44005.27468112332</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>448.0447230416685</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0101816140516868</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.010181614051686935</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>54.542516631</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.288842105264371</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>194.46529432672526</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>54.542516631</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>195.76285180367066</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$66,A4,'Species'!$U$2:$U$66))</x:f>
-        <x:v>10677.398600233695</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.288842105264371</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>194.46529432672526</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>10606.626549967721</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>70.77205026597403</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0066724372667</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.006672437266699977</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1587.9243897183003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.510322191336808</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>323.83381138775326</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1587.9243897183003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>437.115754780224</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$66,A5,'Species'!$U$2:$U$66))</x:f>
-        <x:v>694106.7681456414</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.510322191336808</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>323.83381138775326</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>514223.60731804924</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>179883.1608275922</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.3498150576279042</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.3498150576279042</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3819.0416549555007</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.802154993382712</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>634.0959705075995</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3819.0416549555007</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>879.1639478660655</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$66,A6,'Species'!$U$2:$U$66))</x:f>
-        <x:v>3357563.7384356307</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.802154993382712</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>634.0959705075995</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2421638.9246079572</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>935924.8138276734</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.386484047773221</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.38648404777322104</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>502.1894265653</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.9498684191157056</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>890.980951228549</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>502.1894265653</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>932.0711308480015</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$66,A7,'Species'!$U$2:$U$66))</x:f>
-        <x:v>468076.2667186286</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.9498684191157056</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>890.980951228549</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>447441.21297807054</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>20635.05374055804</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0461179103355627</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04611791033556263</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>114.19828986259999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.426877518021592</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2672.252659849136</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>114.19828986259999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2698.0699785238567</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$66,A8,'Species'!$U$2:$U$66))</x:f>
-        <x:v>308114.9774770463</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.426877518021592</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2672.252659849136</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>305166.68383555545</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2948.293641490862</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0096612566104353</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.009661256610435242</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaa43dabe5af4d3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf74d3ad870d048fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5527,20 +5182,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5548,984 +5193,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>158.8847222984</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.4600000000000004</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>288.40315031266084</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>158.8847222984</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$66,A2,'Species'!$U$2:$U$66))</x:f>
-        <x:v>45822.854447410784</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.4600000000000004</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>288.40315031266084</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>45822.85444741083</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>-4.3655745685100555e-11</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>-9.527068143518344e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2.0432985008</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2.0432985008</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$66,A3,'Species'!$U$2:$U$66))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4470.250046323893</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4470.250046323893</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>141.2348479243</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.212320468703742</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1630.4987443972846</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>141.2348479243</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1782.8268568274607</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$66,A4,'Species'!$U$2:$U$66))</x:f>
-        <x:v>251797.2799993842</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.212320468703742</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1630.4987443972846</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>230283.24220571257</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>21514.037793671625</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0934242439337079</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.09342424393370788</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>209.22831691930003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.435710626186908</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2727.160049200338</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>209.22831691930003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2759.390928256896</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$66,A5,'Species'!$U$2:$U$66))</x:f>
-        <x:v>577342.7196415754</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.435710626186908</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2727.160049200338</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>570599.1070637422</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6743.612577833119</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0118184772712584</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0118184772712583</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>18.027859656</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.65007726834059</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>446.76307179418154</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>18.027859656</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>449.15279492343046</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$66,A6,'Species'!$U$2:$U$66))</x:f>
-        <x:v>8097.263550979754</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.65007726834059</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>446.76307179418154</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8054.181957788957</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>43.08159319079641</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.005348971927451</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.005348971927451117</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>202.469546591</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.8049975821057376</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>638.2599327276577</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>202.469546591</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>655.9476528948506</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$66,A7,'Species'!$U$2:$U$66))</x:f>
-        <x:v>132809.42386905107</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.8049975821057376</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>638.2599327276577</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>129228.19918657102</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3581.224682480053</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0277124087855602</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.027712408785560194</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>435.2754961814</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.003825066561358</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1008.8464417573617</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>435.2754961814</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1014.05441225475</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$66,A8,'Species'!$U$2:$U$66))</x:f>
-        <x:v>441393.03744912427</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.003825066561358</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1008.8464417573617</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>439126.13550677546</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2266.901942348806</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0051623024890848</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.005162302489084778</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4283.154792375801</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6703049195976014</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>468.0636549945633</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4283.154792375801</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>656.2854574958902</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$66,A9,'Species'!$U$2:$U$66))</x:f>
-        <x:v>2810972.202440067</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6703049195976014</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>468.0636549945633</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2004789.0870268974</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>806183.1154131698</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.4021286431725042</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.4021286431725043</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>82.5187615972</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.021732100780665</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1051.313159937595</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>82.5187615972</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1053.4043819477595</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$66,A10,'Species'!$U$2:$U$66))</x:f>
-        <x:v>86925.62505939297</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.021732100780665</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1051.313159937595</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>86753.06000888938</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>172.56505050358828</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0019891523190756</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0019891523190756146</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>142.41729532920002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.012498861808191</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1029.1978298862105</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>142.41729532920002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1029.8504334604418</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$66,A11,'Species'!$U$2:$U$66))</x:f>
-        <x:v>146668.5133270404</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.012498861808191</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1029.1978298862105</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>146575.5712910762</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>92.94203596419538</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0006340895358314</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0006340895358314996</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>280.7880275901</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.754489502744523</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>56.81846579025754</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>280.7880275901</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>56.86204486704058</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$66,A12,'Species'!$U$2:$U$66))</x:f>
-        <x:v>15966.181422956095</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.754489502744523</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>56.81846579025754</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>15953.944939941988</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>12.236483014106852</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.000766987918046</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0007669879180460144</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>12.3762836339</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.03</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>107.1519305237606</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>12.3762836339</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$66,A13,'Species'!$U$2:$U$66))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1326.1426840820081</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.03</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>1326.1426840820081</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>122.2151768197</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.085833333440018</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1218.5218844295298</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>122.2151768197</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1940.643636554138</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$66,A14,'Species'!$U$2:$U$66))</x:f>
-        <x:v>237176.1051854896</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.085833333440018</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1218.5218844295298</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>148921.86756422903</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>88254.23762126057</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.592621077513664</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.592621077513664</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>74.542516631</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.275737609341286</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>188.6851013005144</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>74.542516631</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>189.8648033013503</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$66,A15,'Species'!$U$2:$U$66))</x:f>
-        <x:v>14153.000257732449</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.275737609341286</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>188.6851013005144</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>14065.062301715514</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>87.93795601693455</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0062522265547453</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.006252226554745425</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>144.62129254680002</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.6149295774683545</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>412.03070130666913</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>144.62129254680002</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>421.7827446208379</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$66,A16,'Species'!$U$2:$U$66))</x:f>
-        <x:v>60998.76570100244</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.6149295774683545</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>412.03070130666913</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>59588.412591934975</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1410.353109067466</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.023668244340148</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.023668244340147953</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>104.9707919169</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6224362626007283</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>419.2144679251353</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>104.9707919169</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>423.4827478424323</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$66,A17,'Species'!$U$2:$U$66))</x:f>
-        <x:v>44453.31940416499</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6224362626007283</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>419.2144679251353</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>44005.27468112332</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>448.0447230416685</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0101816140516868</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.010181614051686935</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>48.8860707279</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.5800000000000005</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>380.1893963205616</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>48.8860707279</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>380.1893963205613</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$66,A18,'Species'!$U$2:$U$66))</x:f>
-        <x:v>18585.965718524563</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.5800000000000005</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>380.1893963205616</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>18585.965718524578</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>-1.4551915228366852e-11</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>0.9999999999999992</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>-7.82951795389518e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96bcbb3eb81b4e15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R436ca5b46e384b3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6700,7 +5706,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6799,7 +5805,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>4898958.650204303</x:v>
+        <x:v>3759036.2749106656</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6813,7 +5819,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>4898958.650204302</x:v>
+        <x:v>3968148.359222739</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6827,7 +5833,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-1139922.3752936372</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6841,7 +5847,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-9.313225746154785e-10</x:v>
+        <x:v>-930810.2909815637</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6852,9 +5858,9 @@
         <x:v>EEZ_254</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6866,47 +5872,19 @@
         <x:v>EEZ_254</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_254</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_254</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d2ee6f999d34cba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd1dee8973bd44bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6953,7 +5931,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
